--- a/public/outils/matrices/calculateur-rentabilite-locative.xlsx
+++ b/public/outils/matrices/calculateur-rentabilite-locative.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="445">
   <si>
-    <t>CorpusImmo  ·  corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
+    <t>CorpusImmo  ·  www.corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
   </si>
   <si>
     <t>Mode d'emploi</t>
@@ -54,7 +54,7 @@
     <t>Il calcule le coût complet de l'achat, le loyer réellement encaissé, la mensualité du prêt, l'impôt de la première année selon cinq régimes fiscaux (location nue au micro-foncier ou au réel, meublé au micro-BIC ou au LMNP réel avec amortissement, meublé de tourisme non classé), puis trois rendements et le cash-flow mensuel après impôt.</t>
   </si>
   <si>
-    <t>Tout tient sur un seul onglet de saisie. Le classeur est livré avec un exemple déjà saisi : pour votre dossier, remplacez toutes les cellules bleues, y compris celles qui ne vous concernent pas (mettez 0 : mobilier en location nue, comptable sans expert-comptable, travaux déductibles sans travaux). Le reste se calcule.</t>
+    <t>Tout tient sur un seul onglet de saisie. Le classeur est livré avec un exemple déjà saisi : pour votre dossier, remplacez toutes les cellules violettes, y compris celles qui ne vous concernent pas (mettez 0 : mobilier en location nue, comptable sans expert-comptable, travaux déductibles sans travaux). Le reste se calcule.</t>
   </si>
   <si>
     <t>Vous êtes</t>
@@ -156,7 +156,7 @@
     <t>Ce que vous faites</t>
   </si>
   <si>
-    <t>Fond bleu clair</t>
+    <t>Fond violet clair</t>
   </si>
   <si>
     <t>Saisie utilisateur</t>
@@ -174,7 +174,7 @@
     <t>Vous la lisez. Elle est verrouillée.</t>
   </si>
   <si>
-    <t>Fond bleu pâle, gras</t>
+    <t>Fond violet pâle, gras</t>
   </si>
   <si>
     <t>Résultat de bloc, chiffre clé</t>
@@ -183,7 +183,7 @@
     <t>Vous la lisez. C'est un chiffre à retenir.</t>
   </si>
   <si>
-    <t>Bandeau bleu nuit</t>
+    <t>Bandeau violet</t>
   </si>
   <si>
     <t>Titre de section</t>
@@ -201,7 +201,7 @@
     <t>Une phrase par ligne pour savoir quoi saisir. Les ordres de grandeur y sont lus dans Paramètres.</t>
   </si>
   <si>
-    <t>Cellule bleue qui affiche un %</t>
+    <t>Cellule violette qui affiche un %</t>
   </si>
   <si>
     <t>Taux</t>
@@ -219,7 +219,7 @@
     <t>Rouge : corrigez la saisie indiquée dans le commentaire.</t>
   </si>
   <si>
-    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. En usage normal, vous n'en avez jamais besoin : toutes les cellules bleues sont déjà libres. Pour modifier une cellule blanche ou un texte de source : onglet Révision, puis « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
+    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. En usage normal, vous n'en avez jamais besoin : toutes les cellules violettes sont déjà libres. Pour modifier une cellule blanche ou un texte de source : onglet Révision, puis « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
   </si>
   <si>
     <t xml:space="preserve">  LA MARCHE À SUIVRE, ÉTAPE PAR ÉTAPE</t>
@@ -237,10 +237,10 @@
     <t>0. L'exemple livré</t>
   </si>
   <si>
-    <t>Calculateur, toutes les cellules bleues</t>
-  </si>
-  <si>
-    <t>Le classeur arrive rempli d'un exemple (appartement de 72 m² loué meublé). Gardez-le pour vous repérer, ou effacez toutes les cellules bleues avant de saisir votre dossier. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être dans votre cas : mobilier (C11), comptabilité (C26), travaux déductibles (C49), part du terrain (C50).</t>
+    <t>Calculateur, toutes les cellules violettes</t>
+  </si>
+  <si>
+    <t>Le classeur arrive rempli d'un exemple (appartement de 72 m² loué meublé). Gardez-le pour vous repérer, ou effacez toutes les cellules violettes avant de saisir votre dossier. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être dans votre cas : mobilier (C11), comptabilité (C26), travaux déductibles (C49), part du terrain (C50).</t>
   </si>
   <si>
     <t>Une valeur de l'exemple oubliée est l'erreur la plus probable d'un premier usage. Le contrôle C60 signale les incohérences (travaux déductibles supérieurs aux travaux), pas les oublis plausibles.</t>
@@ -324,7 +324,7 @@
     <t>Paramètres!C8:C17, C21:C34, C38:C42 et C46:C50</t>
   </si>
   <si>
-    <t>Une fois par an, comparez chaque valeur bleue à sa source (colonne D) et mettez à jour la date en C52 : les mentions « Vérifié le » de Paramètres et de Méthode suivent automatiquement. Si une source change (nouveau texte de loi, nouvelle publication), modifiez son texte en colonne D de Paramètres (cellule verrouillée : Révision, Ôter la protection) ; Méthode le recopie.</t>
+    <t>Une fois par an, comparez chaque valeur violette à sa source (colonne D) et mettez à jour la date en C52 : les mentions « Vérifié le » de Paramètres et de Méthode suivent automatiquement. Si une source change (nouveau texte de loi, nouvelle publication), modifiez son texte en colonne D de Paramètres (cellule verrouillée : Révision, Ôter la protection) ; Méthode le recopie.</t>
   </si>
   <si>
     <t>Un barème périmé fausse l'impôt sans prévenir. Toutes les formules pointent ici, commentaires d'aide compris.</t>
@@ -441,7 +441,7 @@
     <t xml:space="preserve">  LES DONNÉES À METTRE À JOUR, OÙ ET POURQUOI</t>
   </si>
   <si>
-    <t>Deux familles de données. Les barèmes et repères (barèmes fiscaux, plafonds, durées d'amortissement, taux de crédit et ordres de grandeur de référence) changent avec la loi ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée : ils vivent tous dans Paramètres. Les données de projet (prix, loyer, charges, financement, régime) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules bleues bougent.</t>
+    <t>Deux familles de données. Les barèmes et repères (barèmes fiscaux, plafonds, durées d'amortissement, taux de crédit et ordres de grandeur de référence) changent avec la loi ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée : ils vivent tous dans Paramètres. Les données de projet (prix, loyer, charges, financement, régime) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules violettes bougent.</t>
   </si>
   <si>
     <t>Paramètre</t>
@@ -699,7 +699,7 @@
     <t>Rendement brut, net de charges et net-net après impôt, avec le cash-flow réel de la première année.</t>
   </si>
   <si>
-    <t>Cellules bleues : à remplir.  Cellules blanches : calculées automatiquement.</t>
+    <t>Cellules violettes : à remplir.  Cellules blanches : calculées automatiquement.</t>
   </si>
   <si>
     <t xml:space="preserve">  LE BIEN</t>
@@ -1403,7 +1403,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1423,19 +1423,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1447,7 +1447,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1460,12 +1460,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E1A33"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
+        <fgColor rgb="FFF1EEF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1475,7 +1475,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F9FF"/>
+        <fgColor rgb="FFF8F6FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1742,6 +1742,138 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8763000" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8763000" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="11258550" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11258550" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8382000" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8382000" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3057,13 +3189,14 @@
     <mergeCell ref="B36:E36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF3B6EF6"/>
+    <tabColor rgb="FF6C5AB0"/>
   </sheetPr>
   <dimension ref="B1:D70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3809,6 +3942,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
@@ -3869,7 +4003,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor rgb="FFB08C4E"/>
+    <tabColor rgb="FF495669"/>
   </sheetPr>
   <dimension ref="B1:F58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4619,13 +4753,14 @@
     <mergeCell ref="B58:F58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF5A6B8C"/>
+    <tabColor rgb="FF8A93A6"/>
   </sheetPr>
   <dimension ref="B1:C58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5076,5 +5211,6 @@
     <mergeCell ref="B26:C26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>